--- a/data/MI_traits_Est_by_Curtis.xlsx
+++ b/data/MI_traits_Est_by_Curtis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11008"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/essing/Library/CloudStorage/Dropbox/Desktop/Rcode/Metabolic_Index/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B59AFC-C9B8-7D4F-8AB5-DAA09111BE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC18E31C-A9F5-3045-A5E0-EA3EFAA5D05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="33560" windowHeight="27360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="214">
   <si>
     <t xml:space="preserve">    'Acanthephyra acutifrons'</t>
   </si>
@@ -7582,7 +7582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
@@ -7861,9 +7861,6 @@
       <c r="Q4">
         <v>3.1242999999999999</v>
       </c>
-      <c r="R4" t="s">
-        <v>72</v>
-      </c>
       <c r="S4">
         <v>987</v>
       </c>
@@ -8007,9 +8004,6 @@
       <c r="Q6">
         <v>4.5134999999999996</v>
       </c>
-      <c r="R6" t="s">
-        <v>72</v>
-      </c>
       <c r="S6">
         <v>68</v>
       </c>
@@ -8080,9 +8074,6 @@
       <c r="Q7" t="s">
         <v>72</v>
       </c>
-      <c r="R7" t="s">
-        <v>72</v>
-      </c>
       <c r="S7">
         <v>12304</v>
       </c>
@@ -8372,9 +8363,6 @@
       <c r="Q11" t="s">
         <v>72</v>
       </c>
-      <c r="R11" t="s">
-        <v>72</v>
-      </c>
       <c r="S11">
         <v>100</v>
       </c>
@@ -8518,9 +8506,6 @@
       <c r="Q13">
         <v>3.9142000000000001</v>
       </c>
-      <c r="R13" t="s">
-        <v>72</v>
-      </c>
       <c r="S13">
         <v>1280</v>
       </c>
@@ -8591,9 +8576,6 @@
       <c r="Q14" t="s">
         <v>72</v>
       </c>
-      <c r="R14" t="s">
-        <v>72</v>
-      </c>
       <c r="S14">
         <v>281</v>
       </c>
@@ -9393,9 +9375,6 @@
       <c r="Q25" t="s">
         <v>72</v>
       </c>
-      <c r="R25" t="s">
-        <v>72</v>
-      </c>
       <c r="S25">
         <v>0</v>
       </c>
@@ -9611,9 +9590,6 @@
       <c r="Q28" t="s">
         <v>72</v>
       </c>
-      <c r="R28" t="s">
-        <v>72</v>
-      </c>
       <c r="S28">
         <v>0</v>
       </c>
@@ -10340,9 +10316,6 @@
       <c r="Q38" t="s">
         <v>72</v>
       </c>
-      <c r="R38" t="s">
-        <v>72</v>
-      </c>
       <c r="S38">
         <v>0</v>
       </c>
@@ -10851,9 +10824,6 @@
       <c r="Q45" t="s">
         <v>72</v>
       </c>
-      <c r="R45" t="s">
-        <v>72</v>
-      </c>
       <c r="S45">
         <v>145</v>
       </c>
@@ -11360,9 +11330,6 @@
       <c r="Q52" t="s">
         <v>72</v>
       </c>
-      <c r="R52" t="s">
-        <v>72</v>
-      </c>
       <c r="S52">
         <v>0</v>
       </c>
@@ -11724,9 +11691,6 @@
       <c r="Q57" t="s">
         <v>72</v>
       </c>
-      <c r="R57" t="s">
-        <v>72</v>
-      </c>
       <c r="S57">
         <v>0</v>
       </c>
@@ -11797,9 +11761,6 @@
       <c r="Q58" t="s">
         <v>72</v>
       </c>
-      <c r="R58" t="s">
-        <v>72</v>
-      </c>
       <c r="S58">
         <v>81</v>
       </c>
@@ -12451,9 +12412,6 @@
       <c r="Q67">
         <v>6.9173</v>
       </c>
-      <c r="R67" t="s">
-        <v>72</v>
-      </c>
       <c r="S67">
         <v>5247</v>
       </c>
@@ -12816,9 +12774,6 @@
       <c r="Q72" t="s">
         <v>72</v>
       </c>
-      <c r="R72" t="s">
-        <v>72</v>
-      </c>
       <c r="S72">
         <v>7</v>
       </c>
@@ -12889,9 +12844,6 @@
       <c r="Q73">
         <v>2.8637000000000001</v>
       </c>
-      <c r="R73" t="s">
-        <v>72</v>
-      </c>
       <c r="S73">
         <v>19915</v>
       </c>
@@ -12903,6 +12855,18 @@
       </c>
       <c r="V73" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="R75">
+        <f>PERCENTILE(R2:R72, 0.1)</f>
+        <v>1.5192999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="R76">
+        <f>PERCENTILE(R2:R72, 0.9)</f>
+        <v>4.3022999999999998</v>
       </c>
     </row>
   </sheetData>
